--- a/file/table/DAPC_M02A02a_Digitalizacion.xlsx
+++ b/file/table/DAPC_M02A02a_Digitalizacion.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29904"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30512"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A735EA-A856-4AE0-BAAC-3D6DDD19F3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CB1811-D4B7-4E51-9D65-25936168C63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DFC394E3-2F24-4121-95B3-0680CAC2ADA7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2026-02" sheetId="2" r:id="rId1"/>
+    <sheet name="2026-01" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="19">
   <si>
     <t>Estudiante \ Edificio</t>
   </si>
@@ -90,6 +91,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Construcciones a digitalizar 2026-02</t>
   </si>
 </sst>
 </file>
@@ -637,6 +641,378 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{369FDE28-55E4-418C-BE3D-6B66AE472192}">
+  <dimension ref="B2:Q13"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
+    <col min="3" max="13" width="4.33203125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="11.21875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="6">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="6">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="6">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="6">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="8">
+        <v>9</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57FC38F-F852-4EC8-9B18-F49E3B87A119}">
   <dimension ref="B2:Q13"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
